--- a/resources/etsy/files/etsy-int-instrument-panel.xlsx
+++ b/resources/etsy/files/etsy-int-instrument-panel.xlsx
@@ -503,7 +503,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -647,7 +646,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -672,14 +670,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>has views + favourites. Read your click rate (visits/impr) right there.</t>
+          <t>has views + favorites. Read your click rate (visits/impr) right there.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>READING RULE: a rate is a rumour until it has enough sample. Treat ~100</t>
+          <t>READING RULE: a rate is a rumor until it has enough sample. Treat ~100</t>
         </is>
       </c>
     </row>
@@ -725,7 +723,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -776,7 +773,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -897,7 +893,6 @@
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -912,7 +907,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>

--- a/resources/etsy/files/etsy-int-instrument-panel.xlsx
+++ b/resources/etsy/files/etsy-int-instrument-panel.xlsx
@@ -733,7 +733,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
